--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB54ECFD-6DAD-49D0-9BA5-18E82B49B4CA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EE4C96-6584-4632-8E47-1B4941AECCC5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="154">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -518,10 +518,13 @@
     <t>CodeGraph</t>
   </si>
   <si>
-    <t>площадь или периметр треугольника (Беймель)</t>
-  </si>
-  <si>
     <t>калькулятор</t>
+  </si>
+  <si>
+    <t>17 Мавзовин, калькулятор</t>
+  </si>
+  <si>
+    <t>площадь и периметрпрямоугольника</t>
   </si>
 </sst>
 </file>
@@ -661,7 +664,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -824,6 +827,12 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -834,9 +843,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1148,68 +1154,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="14.45" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="63"/>
-      <c r="T1" s="63"/>
-      <c r="U1" s="63"/>
-      <c r="V1" s="63"/>
-      <c r="W1" s="63"/>
-      <c r="X1" s="63"/>
-      <c r="Y1" s="63"/>
-      <c r="Z1" s="63"/>
-      <c r="AA1" s="63"/>
-      <c r="AB1" s="63"/>
-      <c r="AC1" s="63"/>
-      <c r="AD1" s="63"/>
-      <c r="AE1" s="63"/>
-      <c r="AF1" s="63"/>
-      <c r="AG1" s="63"/>
-      <c r="AH1" s="63"/>
-      <c r="AI1" s="63"/>
-      <c r="AJ1" s="63"/>
-      <c r="AK1" s="63"/>
-      <c r="AL1" s="63"/>
-      <c r="AM1" s="63"/>
-      <c r="AN1" s="63"/>
-      <c r="AO1" s="63"/>
-      <c r="AP1" s="63"/>
-      <c r="AQ1" s="63"/>
-      <c r="AR1" s="63"/>
-      <c r="AS1" s="63"/>
-      <c r="AT1" s="63"/>
-      <c r="AU1" s="63"/>
-      <c r="AV1" s="63"/>
-      <c r="AW1" s="63"/>
-      <c r="AX1" s="63"/>
-      <c r="AY1" s="63"/>
-      <c r="AZ1" s="63"/>
-      <c r="BA1" s="63"/>
-      <c r="BB1" s="63"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="65"/>
+      <c r="AB1" s="65"/>
+      <c r="AC1" s="65"/>
+      <c r="AD1" s="65"/>
+      <c r="AE1" s="65"/>
+      <c r="AF1" s="65"/>
+      <c r="AG1" s="65"/>
+      <c r="AH1" s="65"/>
+      <c r="AI1" s="65"/>
+      <c r="AJ1" s="65"/>
+      <c r="AK1" s="65"/>
+      <c r="AL1" s="65"/>
+      <c r="AM1" s="65"/>
+      <c r="AN1" s="65"/>
+      <c r="AO1" s="65"/>
+      <c r="AP1" s="65"/>
+      <c r="AQ1" s="65"/>
+      <c r="AR1" s="65"/>
+      <c r="AS1" s="65"/>
+      <c r="AT1" s="65"/>
+      <c r="AU1" s="65"/>
+      <c r="AV1" s="65"/>
+      <c r="AW1" s="65"/>
+      <c r="AX1" s="65"/>
+      <c r="AY1" s="65"/>
+      <c r="AZ1" s="65"/>
+      <c r="BA1" s="65"/>
+      <c r="BB1" s="65"/>
     </row>
     <row r="2" spans="1:54" ht="27.6" customHeight="1">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="65"/>
+      <c r="B2" s="67"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -2055,10 +2061,12 @@
       <c r="AL8" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="AM8" s="3">
-        <v>17</v>
-      </c>
-      <c r="AN8" s="62"/>
+      <c r="AM8" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="AN8" s="24">
+        <v>46182</v>
+      </c>
       <c r="AP8" s="42" t="s">
         <v>72</v>
       </c>
@@ -2068,7 +2076,9 @@
       <c r="AR8" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="AS8" s="3"/>
+      <c r="AS8" s="24">
+        <v>46182</v>
+      </c>
       <c r="AT8" s="30"/>
       <c r="AU8" s="62" t="s">
         <v>150</v>
@@ -2077,8 +2087,10 @@
         <v>46177</v>
       </c>
       <c r="AW8" s="3"/>
-      <c r="AX8" s="3"/>
-      <c r="AY8" s="3"/>
+      <c r="AX8" s="24">
+        <v>46182</v>
+      </c>
+      <c r="AY8" s="59"/>
       <c r="AZ8" s="3"/>
       <c r="BA8" s="3"/>
       <c r="BB8" s="1"/>
@@ -2785,7 +2797,9 @@
       <c r="C14" s="9">
         <v>11</v>
       </c>
-      <c r="D14" s="9"/>
+      <c r="D14" s="63" t="s">
+        <v>153</v>
+      </c>
       <c r="E14" s="9" t="s">
         <v>16</v>
       </c>
@@ -2858,7 +2872,9 @@
         <v>46177</v>
       </c>
       <c r="AD14" s="3"/>
-      <c r="AE14" s="3"/>
+      <c r="AE14" s="24">
+        <v>46182</v>
+      </c>
       <c r="AF14" s="3"/>
       <c r="AG14" s="3"/>
       <c r="AH14" s="3"/>
@@ -3656,9 +3672,13 @@
       <c r="AD20" s="3"/>
       <c r="AE20" s="3"/>
       <c r="AF20" s="3"/>
-      <c r="AG20" s="3"/>
+      <c r="AG20" s="24">
+        <v>46182</v>
+      </c>
       <c r="AH20" s="3"/>
-      <c r="AI20" s="3"/>
+      <c r="AI20" s="24">
+        <v>46182</v>
+      </c>
       <c r="AJ20" s="3">
         <v>2</v>
       </c>
@@ -3693,7 +3713,7 @@
       <c r="BA20" s="3"/>
       <c r="BB20" s="1"/>
     </row>
-    <row r="21" spans="1:54" ht="120">
+    <row r="21" spans="1:54" ht="105">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -3793,25 +3813,36 @@
         <v>3</v>
       </c>
       <c r="AK21" s="30"/>
-      <c r="AM21" s="3"/>
-      <c r="AN21" s="62"/>
-      <c r="AO21" s="49" t="s">
-        <v>151</v>
-      </c>
-      <c r="AP21" s="30"/>
-      <c r="AQ21" s="3"/>
-      <c r="AR21" s="3"/>
-      <c r="AS21" s="3"/>
+      <c r="AM21" s="63" t="s">
+        <v>152</v>
+      </c>
+      <c r="AN21" s="24">
+        <v>46182</v>
+      </c>
+      <c r="AP21" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ21" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR21" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="AS21" s="24">
+        <v>46182</v>
+      </c>
       <c r="AT21" s="30"/>
-      <c r="AU21" s="62" t="s">
+      <c r="AU21" s="63" t="s">
         <v>150</v>
       </c>
       <c r="AV21" s="24">
         <v>46177</v>
       </c>
-      <c r="AW21" s="3"/>
-      <c r="AX21" s="3"/>
-      <c r="AY21" s="3"/>
+      <c r="AW21" s="63"/>
+      <c r="AX21" s="24">
+        <v>46182</v>
+      </c>
+      <c r="AY21" s="59"/>
       <c r="AZ21" s="3"/>
       <c r="BA21" s="3"/>
       <c r="BB21" s="1"/>
@@ -4086,7 +4117,7 @@
       <c r="BA23" s="3"/>
       <c r="BB23" s="1"/>
     </row>
-    <row r="24" spans="1:54" ht="120">
+    <row r="24" spans="1:54" ht="135">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -4212,10 +4243,14 @@
       <c r="AU24" s="49" t="s">
         <v>148</v>
       </c>
-      <c r="AV24" s="3"/>
+      <c r="AV24" s="24">
+        <v>46182</v>
+      </c>
       <c r="AW24" s="3"/>
-      <c r="AX24" s="3"/>
-      <c r="AY24" s="3"/>
+      <c r="AX24" s="24">
+        <v>46182</v>
+      </c>
+      <c r="AY24" s="59"/>
       <c r="AZ24" s="3"/>
       <c r="BA24" s="3"/>
       <c r="BB24" s="1"/>
@@ -4362,8 +4397,8 @@
       <c r="C26" s="9">
         <v>18</v>
       </c>
-      <c r="D26" s="67" t="s">
-        <v>152</v>
+      <c r="D26" s="64" t="s">
+        <v>151</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>17</v>
@@ -5149,7 +5184,7 @@
       <c r="BA31" s="3"/>
       <c r="BB31" s="1"/>
     </row>
-    <row r="32" spans="1:54" ht="120">
+    <row r="32" spans="1:54" ht="135">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -5273,10 +5308,14 @@
       <c r="AU32" s="49" t="s">
         <v>148</v>
       </c>
-      <c r="AV32" s="3"/>
-      <c r="AW32" s="3"/>
-      <c r="AX32" s="3"/>
-      <c r="AY32" s="3"/>
+      <c r="AV32" s="24">
+        <v>46182</v>
+      </c>
+      <c r="AW32" s="63"/>
+      <c r="AX32" s="24">
+        <v>46182</v>
+      </c>
+      <c r="AY32" s="59"/>
       <c r="AZ32" s="3"/>
       <c r="BA32" s="3"/>
       <c r="BB32" s="1"/>
@@ -6113,56 +6152,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="63"/>
-      <c r="T1" s="63"/>
-      <c r="U1" s="63"/>
-      <c r="V1" s="63"/>
-      <c r="W1" s="63"/>
-      <c r="X1" s="63"/>
-      <c r="Y1" s="63"/>
-      <c r="Z1" s="63"/>
-      <c r="AA1" s="63"/>
-      <c r="AB1" s="63"/>
-      <c r="AC1" s="63"/>
-      <c r="AD1" s="63"/>
-      <c r="AE1" s="63"/>
-      <c r="AF1" s="63"/>
-      <c r="AG1" s="63"/>
-      <c r="AH1" s="63"/>
-      <c r="AI1" s="63"/>
-      <c r="AJ1" s="63"/>
-      <c r="AK1" s="63"/>
-      <c r="AL1" s="63"/>
-      <c r="AM1" s="63"/>
-      <c r="AN1" s="63"/>
-      <c r="AO1" s="63"/>
-      <c r="AP1" s="63"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="65"/>
+      <c r="AB1" s="65"/>
+      <c r="AC1" s="65"/>
+      <c r="AD1" s="65"/>
+      <c r="AE1" s="65"/>
+      <c r="AF1" s="65"/>
+      <c r="AG1" s="65"/>
+      <c r="AH1" s="65"/>
+      <c r="AI1" s="65"/>
+      <c r="AJ1" s="65"/>
+      <c r="AK1" s="65"/>
+      <c r="AL1" s="65"/>
+      <c r="AM1" s="65"/>
+      <c r="AN1" s="65"/>
+      <c r="AO1" s="65"/>
+      <c r="AP1" s="65"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="65"/>
+      <c r="B2" s="67"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -6591,142 +6630,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="65">
+      <c r="A11" s="67">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="65"/>
-      <c r="K11" s="65"/>
-      <c r="L11" s="66"/>
-      <c r="M11" s="66"/>
-      <c r="N11" s="66"/>
-      <c r="O11" s="66"/>
-      <c r="P11" s="66"/>
-      <c r="Q11" s="66"/>
-      <c r="R11" s="66"/>
-      <c r="S11" s="66"/>
-      <c r="T11" s="66"/>
-      <c r="U11" s="66"/>
-      <c r="V11" s="66"/>
-      <c r="W11" s="66"/>
-      <c r="X11" s="66"/>
-      <c r="Y11" s="66"/>
-      <c r="Z11" s="66"/>
-      <c r="AA11" s="66"/>
-      <c r="AB11" s="66"/>
-      <c r="AC11" s="66"/>
-      <c r="AD11" s="66"/>
-      <c r="AE11" s="66"/>
-      <c r="AF11" s="66"/>
-      <c r="AG11" s="66"/>
-      <c r="AH11" s="66"/>
-      <c r="AI11" s="66"/>
-      <c r="AJ11" s="66"/>
-      <c r="AK11" s="66"/>
-      <c r="AL11" s="66"/>
-      <c r="AM11" s="66"/>
-      <c r="AN11" s="66"/>
-      <c r="AO11" s="66"/>
-      <c r="AP11" s="63"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="68"/>
+      <c r="M11" s="68"/>
+      <c r="N11" s="68"/>
+      <c r="O11" s="68"/>
+      <c r="P11" s="68"/>
+      <c r="Q11" s="68"/>
+      <c r="R11" s="68"/>
+      <c r="S11" s="68"/>
+      <c r="T11" s="68"/>
+      <c r="U11" s="68"/>
+      <c r="V11" s="68"/>
+      <c r="W11" s="68"/>
+      <c r="X11" s="68"/>
+      <c r="Y11" s="68"/>
+      <c r="Z11" s="68"/>
+      <c r="AA11" s="68"/>
+      <c r="AB11" s="68"/>
+      <c r="AC11" s="68"/>
+      <c r="AD11" s="68"/>
+      <c r="AE11" s="68"/>
+      <c r="AF11" s="68"/>
+      <c r="AG11" s="68"/>
+      <c r="AH11" s="68"/>
+      <c r="AI11" s="68"/>
+      <c r="AJ11" s="68"/>
+      <c r="AK11" s="68"/>
+      <c r="AL11" s="68"/>
+      <c r="AM11" s="68"/>
+      <c r="AN11" s="68"/>
+      <c r="AO11" s="68"/>
+      <c r="AP11" s="65"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="65"/>
+      <c r="A12" s="67"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="65"/>
-      <c r="F12" s="65"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
-      <c r="I12" s="65"/>
-      <c r="J12" s="65"/>
-      <c r="K12" s="65"/>
-      <c r="L12" s="66"/>
-      <c r="M12" s="66"/>
-      <c r="N12" s="66"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="66"/>
-      <c r="S12" s="66"/>
-      <c r="T12" s="66"/>
-      <c r="U12" s="66"/>
-      <c r="V12" s="66"/>
-      <c r="W12" s="66"/>
-      <c r="X12" s="66"/>
-      <c r="Y12" s="66"/>
-      <c r="Z12" s="66"/>
-      <c r="AA12" s="66"/>
-      <c r="AB12" s="66"/>
-      <c r="AC12" s="66"/>
-      <c r="AD12" s="66"/>
-      <c r="AE12" s="66"/>
-      <c r="AF12" s="66"/>
-      <c r="AG12" s="66"/>
-      <c r="AH12" s="66"/>
-      <c r="AI12" s="66"/>
-      <c r="AJ12" s="66"/>
-      <c r="AK12" s="66"/>
-      <c r="AL12" s="66"/>
-      <c r="AM12" s="66"/>
-      <c r="AN12" s="66"/>
-      <c r="AO12" s="66"/>
-      <c r="AP12" s="63"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
+      <c r="L12" s="68"/>
+      <c r="M12" s="68"/>
+      <c r="N12" s="68"/>
+      <c r="O12" s="68"/>
+      <c r="P12" s="68"/>
+      <c r="Q12" s="68"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="68"/>
+      <c r="T12" s="68"/>
+      <c r="U12" s="68"/>
+      <c r="V12" s="68"/>
+      <c r="W12" s="68"/>
+      <c r="X12" s="68"/>
+      <c r="Y12" s="68"/>
+      <c r="Z12" s="68"/>
+      <c r="AA12" s="68"/>
+      <c r="AB12" s="68"/>
+      <c r="AC12" s="68"/>
+      <c r="AD12" s="68"/>
+      <c r="AE12" s="68"/>
+      <c r="AF12" s="68"/>
+      <c r="AG12" s="68"/>
+      <c r="AH12" s="68"/>
+      <c r="AI12" s="68"/>
+      <c r="AJ12" s="68"/>
+      <c r="AK12" s="68"/>
+      <c r="AL12" s="68"/>
+      <c r="AM12" s="68"/>
+      <c r="AN12" s="68"/>
+      <c r="AO12" s="68"/>
+      <c r="AP12" s="65"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="65"/>
+      <c r="A13" s="67"/>
       <c r="B13" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="65"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="65"/>
-      <c r="K13" s="65"/>
-      <c r="L13" s="66"/>
-      <c r="M13" s="66"/>
-      <c r="N13" s="66"/>
-      <c r="O13" s="66"/>
-      <c r="P13" s="66"/>
-      <c r="Q13" s="66"/>
-      <c r="R13" s="66"/>
-      <c r="S13" s="66"/>
-      <c r="T13" s="66"/>
-      <c r="U13" s="66"/>
-      <c r="V13" s="66"/>
-      <c r="W13" s="66"/>
-      <c r="X13" s="66"/>
-      <c r="Y13" s="66"/>
-      <c r="Z13" s="66"/>
-      <c r="AA13" s="66"/>
-      <c r="AB13" s="66"/>
-      <c r="AC13" s="66"/>
-      <c r="AD13" s="66"/>
-      <c r="AE13" s="66"/>
-      <c r="AF13" s="66"/>
-      <c r="AG13" s="66"/>
-      <c r="AH13" s="66"/>
-      <c r="AI13" s="66"/>
-      <c r="AJ13" s="66"/>
-      <c r="AK13" s="66"/>
-      <c r="AL13" s="66"/>
-      <c r="AM13" s="66"/>
-      <c r="AN13" s="66"/>
-      <c r="AO13" s="66"/>
-      <c r="AP13" s="63"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="67"/>
+      <c r="L13" s="68"/>
+      <c r="M13" s="68"/>
+      <c r="N13" s="68"/>
+      <c r="O13" s="68"/>
+      <c r="P13" s="68"/>
+      <c r="Q13" s="68"/>
+      <c r="R13" s="68"/>
+      <c r="S13" s="68"/>
+      <c r="T13" s="68"/>
+      <c r="U13" s="68"/>
+      <c r="V13" s="68"/>
+      <c r="W13" s="68"/>
+      <c r="X13" s="68"/>
+      <c r="Y13" s="68"/>
+      <c r="Z13" s="68"/>
+      <c r="AA13" s="68"/>
+      <c r="AB13" s="68"/>
+      <c r="AC13" s="68"/>
+      <c r="AD13" s="68"/>
+      <c r="AE13" s="68"/>
+      <c r="AF13" s="68"/>
+      <c r="AG13" s="68"/>
+      <c r="AH13" s="68"/>
+      <c r="AI13" s="68"/>
+      <c r="AJ13" s="68"/>
+      <c r="AK13" s="68"/>
+      <c r="AL13" s="68"/>
+      <c r="AM13" s="68"/>
+      <c r="AN13" s="68"/>
+      <c r="AO13" s="68"/>
+      <c r="AP13" s="65"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -7882,6 +7921,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -7898,33 +7964,6 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
